--- a/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/contract_risks.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/contract_risks.xlsx
@@ -479,17 +479,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Auto-renew</t>
+          <t>Lock-in</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -501,17 +501,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lock-in</t>
+          <t>Termination</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -545,17 +545,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auto-renew</t>
+          <t>SLA gap</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -589,17 +589,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lock-in</t>
+          <t>Price escalation</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -611,17 +611,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SLA gap</t>
+          <t>Price escalation</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -633,17 +633,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lock-in</t>
+          <t>Termination</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -655,17 +655,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SLA gap</t>
+          <t>Price escalation</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Auto-renew</t>
+          <t>Termination</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Price escalation</t>
+          <t>Auto-renew</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auto-renew</t>
+          <t>Lock-in</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Price escalation</t>
+          <t>SLA gap</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SLA gap</t>
+          <t>Auto-renew</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auto-renew</t>
+          <t>Termination</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -875,17 +875,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Termination</t>
+          <t>SLA gap</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Price escalation</t>
+          <t>Termination</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
